--- a/NURBS IDX11 PYTHON ANALYSIS/8_4_2026_Redo_front/15gps/3mps_15gps_analysis.xlsx
+++ b/NURBS IDX11 PYTHON ANALYSIS/8_4_2026_Redo_front/15gps/3mps_15gps_analysis.xlsx
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>433.351826473298</v>
+        <v>433.3851235729551</v>
       </c>
       <c r="X3">
         <v>0.247174566</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>23.41105088673355</v>
+        <v>23.41140021852875</v>
       </c>
       <c r="X5">
         <v>0.247144078</v>
@@ -1299,7 +1299,7 @@
         <v>430.3883846038147</v>
       </c>
       <c r="V10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
         <v>0.24709358</v>
